--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,29 +547,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -579,22 +579,22 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -643,29 +643,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -675,29 +675,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -707,22 +707,22 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -744,17 +744,17 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -771,20 +771,84 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -552,24 +552,24 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -611,29 +611,29 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -643,22 +643,22 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -675,22 +675,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -707,29 +707,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -739,29 +739,29 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -771,22 +771,22 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -808,17 +808,17 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -835,20 +835,84 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,29 +547,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -616,24 +616,24 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -653,19 +653,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -675,29 +675,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -707,22 +707,22 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -771,29 +771,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -803,29 +803,29 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -835,22 +835,22 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -899,20 +899,84 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,22 +547,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
@@ -579,29 +579,29 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -611,22 +611,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
@@ -643,29 +643,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -675,22 +675,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
@@ -707,29 +707,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -739,22 +739,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -771,22 +771,22 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
@@ -835,29 +835,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
         </is>
       </c>
     </row>
@@ -963,20 +963,52 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,29 +547,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -579,29 +579,29 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -621,19 +621,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -643,29 +643,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -675,29 +675,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -707,29 +707,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -739,29 +739,29 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -771,29 +771,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -803,29 +803,29 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -835,22 +835,22 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -867,29 +867,29 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -899,29 +899,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -931,29 +931,29 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -963,22 +963,22 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -995,20 +995,116 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,64 +537,64 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
@@ -611,29 +611,29 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -643,29 +643,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -675,29 +675,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -712,24 +712,24 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -739,29 +739,29 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -808,24 +808,24 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -845,19 +845,19 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -867,29 +867,29 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -899,22 +899,22 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -931,22 +931,22 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -963,29 +963,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -995,29 +995,29 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -1091,20 +1091,84 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -552,24 +552,24 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -589,76 +589,76 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
@@ -675,29 +675,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -707,29 +707,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -739,29 +739,29 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -803,29 +803,29 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -845,19 +845,19 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -872,24 +872,24 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -909,19 +909,19 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -931,29 +931,29 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -963,22 +963,22 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -995,22 +995,22 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -1027,29 +1027,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1059,29 +1059,29 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -1155,20 +1155,84 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,29 +547,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -616,24 +616,24 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -653,76 +653,76 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
@@ -739,29 +739,29 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -771,29 +771,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -803,29 +803,29 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -840,24 +840,24 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -867,29 +867,29 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -909,19 +909,19 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -936,24 +936,24 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -995,29 +995,29 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1059,22 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -1091,29 +1091,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1123,29 +1123,29 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -1192,17 +1192,17 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -1219,20 +1219,84 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,29 +547,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -611,29 +611,29 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -653,19 +653,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -680,24 +680,24 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -717,76 +717,76 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
@@ -803,29 +803,29 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -835,29 +835,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -867,29 +867,29 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -931,29 +931,29 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1037,19 +1037,19 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1059,29 +1059,29 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -1123,22 +1123,22 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -1155,29 +1155,29 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1187,29 +1187,29 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1219,22 +1219,22 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -1256,17 +1256,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -1283,20 +1283,84 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -557,19 +557,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -611,29 +611,29 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -653,19 +653,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -675,29 +675,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -717,19 +717,19 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -744,24 +744,24 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -781,76 +781,76 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
@@ -867,29 +867,29 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -899,29 +899,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -931,29 +931,29 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -995,29 +995,29 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1037,19 +1037,19 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1064,24 +1064,24 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1101,19 +1101,19 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1123,29 +1123,29 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -1187,22 +1187,22 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
@@ -1219,29 +1219,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1251,29 +1251,29 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1283,22 +1283,22 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -1320,17 +1320,17 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
@@ -1347,20 +1347,84 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jerk Parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes (Simple)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes (Detail)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jerk Parameters" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,11 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -67,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -89,11 +95,16 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +121,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,7 +504,353 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OrcaForCubicon — 릴리스 노트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>최신 버전 1.5.1 (2026-08-11) · OrcaSlicer 2.4.2 기반 · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>배포일</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>주요 변경 사항</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>고객 영향 / 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>G-code 파일 열기 호환성 복원</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>이전 버전(1.4.x)이나 OrcaSlicer 에서 저장한 G-code 를 다시 불러올 수 있습니다. 1.5.0 에서 "OrcaForCubicon 에서 생성한 gcode 파일이 아닙니다" 오류로 열리지 않던 문제를 수정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Mainsail / Moonraker 슬라이싱 정보 표시</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>프린터 웹 UI 에서 슬라이서 이름·버전과 출력 정보가 정상적으로 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>설치</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>새 PC 설치 안정화 (WebView2 런타임 자동 설치)</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>설치 시 필요한 WebView2 런타임을 자동으로 함께 설치합니다. 새 PC 에서 최초 실행 시 설정 마법사가 빈 화면으로 표시되던 문제가 해결됩니다. (VC++ 런타임도 동봉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>출력 정밀도(공차) 기본값 보정</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>코끼리발 보정 및 X-Y 구멍/외곽 보정을 기본 프로파일에 적용했습니다. 구멍 지름과 외곽 치수 정확도가 향상됩니다. (모든 재료 공통 적용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>서포트 · 라프트 · 오버행 기본값 정리</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>서포트 기본 끔, 라프트 0층으로 설정했습니다. 서포트를 켤 경우 유형은 트리(자동), 임계각 30° 가 기본이며 오버행 감지가 켜집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>시작 화면(스플래시) 개선</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>CUBICON 과 Orca 로고를 함께 표시하고 제품명 "OrcaForCubicon" 을 표기합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>출력 품질 개선 — 장비 저크(Jerk) 하향 조정</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Z축 벽면 잔상(고스팅)이 줄어듭니다. xCeler-Plus / I / Mini 공통 적용이며, G-code 에 자동 반영되므로 장비 설정을 따로 바꿀 필요가 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>업데이트 알림</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>새 버전이 배포되면 프로그램 시작 시 안내 팝업이 표시되고, 클릭하면 다운로드 페이지로 이동합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>큐비콘 프로파일 패키지 갱신 (02.03.03.00)</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>기존 설치 사용자에게도 갱신된 큐비콘 장비·재료 프로파일이 전파됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>다크 모드 시작 화면 로고</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>다크 모드에서 구형 "style CUBICON" 로고가 표시되던 문제를 수정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>※ 시험 중인 필라멘트(Rainbow PLA HS, TPU-HS)는 검증 완료 전까지 정식 배포판에 포함되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>※ 다운로드: https://github.com/Hyvision/OrcaForCubicon/releases/latest</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -496,9 +869,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>제품 버전(Product) = 재정의 버전 · Orca base 2.4.2 · 프로파일 패키지 02.03.03.00</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>제품 버전(Product) = 재정의 버전 · Orca base 2.4.2 · 프로파일 패키지 02.03.03.00 · 전체 수정 내역(사내용)</t>
         </is>
       </c>
     </row>
@@ -535,896 +908,992 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>GitHub Release</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>1.5.1-rc8</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Splash</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>1.5.1-rc8</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Chore</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>제품 버전 rc7 → rc8</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc7</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Process profile</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc7</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc6</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Process profile</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc5</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc4</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Process profile</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc4</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Filament profile</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc3</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc2</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>G-code load</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Installer / Runtime</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>1.5.1-rc2</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>1.5.1-rc1</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>version / release</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc5</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Splash</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc5</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc4</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Build / Filament</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc4</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc3</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Update check</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc3</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc2</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>G-code / Mainsail</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc2</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>build_win.ps1</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc2</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>build_win.ps1</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc2</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc1</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Machine profile</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc1</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Filament profile</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>신규 필라멘트: Cubicon TPU-HS</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>1.5.0-rc1</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Feat</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Filament profile</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>1.5.0-rc1</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>
@@ -1435,7 +1904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,6 +138,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,14 +510,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,7 +528,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>최신 버전 1.5.1 (2026-08-11) · OrcaSlicer 2.4.2 기반 · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
+          <t>최신 버전 1.5.1 (2026-08-11) · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
         </is>
       </c>
     </row>
@@ -541,17 +545,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
           <t>주요 변경 사항</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>고객 영향 / 설명</t>
         </is>
       </c>
     </row>
@@ -566,19 +560,9 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>G-code 파일 열기 호환성 복원</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>이전 버전(1.4.x)이나 OrcaSlicer 에서 저장한 G-code 를 다시 불러올 수 있습니다. 1.5.0 에서 "OrcaForCubicon 에서 생성한 gcode 파일이 아닙니다" 오류로 열리지 않던 문제를 수정했습니다.</t>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>이전 버전(1.4.x)·OrcaSlicer 에서 저장한 G-code 파일이 열리지 않던 문제 수정, 새 PC 설치 안정화</t>
         </is>
       </c>
     </row>
@@ -593,247 +577,48 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Mainsail / Moonraker 슬라이싱 정보 표시</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>프린터 웹 UI 에서 슬라이서 이름·버전과 출력 정보가 정상적으로 표시됩니다.</t>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>출력 정밀도(공차) 보정 기본 적용 및 서포트·라프트 기본값 정리</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.0</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>설치</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>새 PC 설치 안정화 (WebView2 런타임 자동 설치)</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>설치 시 필요한 WebView2 런타임을 자동으로 함께 설치합니다. 새 PC 에서 최초 실행 시 설정 마법사가 빈 화면으로 표시되던 문제가 해결됩니다. (VC++ 런타임도 동봉)</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>출력 품질 개선 — Z축 벽면 잔상(고스팅) 저감</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.0</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>출력 정밀도(공차) 기본값 보정</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>코끼리발 보정 및 X-Y 구멍/외곽 보정을 기본 프로파일에 적용했습니다. 구멍 지름과 외곽 치수 정확도가 향상됩니다. (모든 재료 공통 적용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>서포트 · 라프트 · 오버행 기본값 정리</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>서포트 기본 끔, 라프트 0층으로 설정했습니다. 서포트를 켤 경우 유형은 트리(자동), 임계각 30° 가 기본이며 오버행 감지가 켜집니다.</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>새 버전 업데이트 알림 기능 추가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>시작 화면(스플래시) 개선</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>CUBICON 과 Orca 로고를 함께 표시하고 제품명 "OrcaForCubicon" 을 표기합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>1.5.0</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>출력 품질 개선 — 장비 저크(Jerk) 하향 조정</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Z축 벽면 잔상(고스팅)이 줄어듭니다. xCeler-Plus / I / Mini 공통 적용이며, G-code 에 자동 반영되므로 장비 설정을 따로 바꿀 필요가 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>1.5.0</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>업데이트 알림</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>새 버전이 배포되면 프로그램 시작 시 안내 팝업이 표시되고, 클릭하면 다운로드 페이지로 이동합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>1.5.0</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>큐비콘 프로파일 패키지 갱신 (02.03.03.00)</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>기존 설치 사용자에게도 갱신된 큐비콘 장비·재료 프로파일이 전파됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>1.5.0</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>다크 모드 시작 화면 로고</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>다크 모드에서 구형 "style CUBICON" 로고가 표시되던 문제를 수정했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>※ 시험 중인 필라멘트(Rainbow PLA HS, TPU-HS)는 검증 완료 전까지 정식 배포판에 포함되지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>※ 다운로드: https://github.com/Hyvision/OrcaForCubicon/releases/latest</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -695,44 +695,44 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -742,93 +742,93 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -838,125 +838,125 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -971,19 +971,19 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1003,19 +1003,19 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1035,19 +1035,19 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -1062,24 +1062,24 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -1126,93 +1126,93 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1222,61 +1222,61 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -1291,19 +1291,19 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -1313,29 +1313,29 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1345,29 +1345,29 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -1377,29 +1377,29 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1414,24 +1414,24 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1473,29 +1473,29 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -1505,29 +1505,29 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1547,19 +1547,19 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -1574,24 +1574,24 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1601,29 +1601,29 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -1633,52 +1633,244 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
+          <t>1.5.0-rc2</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>build_win.ps1</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>release / test 빌드 유형 옵션 추가</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc2</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>build_win.ps1</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc2</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Chore</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>제품 버전 rc1 → rc2</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
           <t>1.5.0-rc1</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>최신 버전 1.5.1 (2026-08-11) · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
+          <t>최신 버전 1.5.2 (2026-08-19) · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>이전 버전(1.4.x)·OrcaSlicer 에서 저장한 G-code 파일이 열리지 않던 문제 수정, 새 PC 설치 안정화</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>인필 패턴 변경 — 출력 중 노즐 간섭에 따른 소음·출력 실패 개선</t>
         </is>
       </c>
     </row>
@@ -577,26 +577,26 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>출력 정밀도(공차) 보정 기본 적용 및 서포트·라프트 기본값 정리</t>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>이전 버전(1.4.x)·OrcaSlicer 에서 저장한 G-code 파일이 열리지 않던 문제 수정, 새 PC 설치 안정화</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.0</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>출력 품질 개선 — Z축 벽면 잔상(고스팅) 저감</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>출력 정밀도(공차) 보정 기본 적용 및 서포트·라프트 기본값 정리</t>
         </is>
       </c>
     </row>
@@ -611,18 +611,38 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>출력 품질 개선 — Z축 벽면 잔상(고스팅) 저감</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>새 버전 업데이트 알림 기능 추가</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>※ 다운로드: https://github.com/Hyvision/OrcaForCubicon/releases/latest</t>
         </is>
       </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -635,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -695,140 +715,140 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Branding (macOS)</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
+          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
+          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Branding (macOS/Win)</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
+          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
+          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>build_mac.sh / package_mac.sh</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
+          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
+          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Build (macOS)</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
+          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
+          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -838,17 +858,17 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>patches</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
+          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
+          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
         </is>
       </c>
     </row>
@@ -865,130 +885,130 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc8 → rc9</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -998,29 +1018,29 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1035,115 +1055,115 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1158,24 +1178,24 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -1185,29 +1205,29 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1217,29 +1237,29 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -1249,29 +1269,29 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1281,66 +1301,66 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1350,29 +1370,29 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1387,83 +1407,83 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1473,29 +1493,29 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -1510,24 +1530,24 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1547,19 +1567,19 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -1569,29 +1589,29 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1601,29 +1621,29 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -1633,29 +1653,29 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -1665,29 +1685,29 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -1697,29 +1717,29 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1729,29 +1749,29 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -1761,29 +1781,29 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1793,29 +1813,29 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -1825,52 +1845,212 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
+          <t>1.5.0-rc2</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>build_win.ps1</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc2</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Chore</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>제품 버전 rc1 → rc2</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
           <t>1.5.0-rc1</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -634,7 +634,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -655,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,7 +714,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -725,7 +724,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -735,19 +734,19 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
+          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
+          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -757,29 +756,29 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
+          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
+          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -789,22 +788,22 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
+          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
         </is>
       </c>
     </row>
@@ -821,22 +820,22 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
+          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
+          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
         </is>
       </c>
     </row>
@@ -853,118 +852,118 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
+          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
+          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Branding (macOS)</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
+          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
+          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Branding (macOS/Win)</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
+          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
+          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>build_mac.sh / package_mac.sh</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
+          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
+          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
         </is>
       </c>
     </row>
@@ -986,17 +985,17 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Build (macOS)</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
@@ -1013,22 +1012,22 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>patches</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
@@ -1045,98 +1044,98 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc8 → rc9</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -1151,115 +1150,115 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -1274,24 +1273,24 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1301,29 +1300,29 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -1333,29 +1332,29 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1365,29 +1364,29 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -1397,29 +1396,29 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1429,29 +1428,29 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -1461,66 +1460,66 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -1530,29 +1529,29 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -1567,19 +1566,19 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -1589,29 +1588,29 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1621,29 +1620,29 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -1663,19 +1662,19 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -1685,29 +1684,29 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -1717,29 +1716,29 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1749,29 +1748,29 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -1781,29 +1780,29 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1813,29 +1812,29 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -1845,29 +1844,29 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -1877,22 +1876,22 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -1909,29 +1908,29 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -1941,29 +1940,29 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -1973,29 +1972,29 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2005,22 +2004,22 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -2037,20 +2036,116 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>최신 버전 1.5.2 (2026-08-19) · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
+          <t>최신 버전 1.5.3 (2026-08-20) · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
         </is>
       </c>
     </row>
@@ -552,34 +552,34 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>인필 패턴 변경 — 출력 중 노즐 간섭에 따른 소음·출력 실패 개선</t>
+          <t>필라멘트 선택 목록이 비거나 Cubicon 필라멘트 대신 Default Filament 로 선택되던 문제 수정</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>이전 버전(1.4.x)·OrcaSlicer 에서 저장한 G-code 파일이 열리지 않던 문제 수정, 새 PC 설치 안정화</t>
+          <t>인필 패턴 변경 — 출력 중 노즐 간섭에 따른 소음·출력 실패 개선</t>
         </is>
       </c>
     </row>
@@ -596,24 +596,24 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>출력 정밀도(공차) 보정 기본 적용 및 서포트·라프트 기본값 정리</t>
+          <t>이전 버전(1.4.x)·OrcaSlicer 에서 저장한 G-code 파일이 열리지 않던 문제 수정, 새 PC 설치 안정화</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.0</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>출력 품질 개선 — Z축 벽면 잔상(고스팅) 저감</t>
+          <t>출력 정밀도(공차) 보정 기본 적용 및 서포트·라프트 기본값 정리</t>
         </is>
       </c>
     </row>
@@ -630,18 +630,36 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
+          <t>출력 품질 개선 — Z축 벽면 잔상(고스팅) 저감</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
           <t>새 버전 업데이트 알림 기능 추가</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>※ 다운로드: https://github.com/Hyvision/OrcaForCubicon/releases/latest</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -654,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -714,44 +732,44 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.3-rc1</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
+          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
+          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.3-rc1</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -761,29 +779,29 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
+          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
+          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.3-rc1</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -798,19 +816,19 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>기본 버전 1.5.2 → 1.5.3 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
+          <t>v1.5.2 GitHub 릴리스 발행 완료에 따라 1.5.3-rc1 로 전환.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -820,7 +838,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -830,19 +848,19 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
+          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
+          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -852,29 +870,29 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
+          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
+          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -884,22 +902,22 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
+          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
         </is>
       </c>
     </row>
@@ -916,22 +934,22 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
+          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
+          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
         </is>
       </c>
     </row>
@@ -948,118 +966,118 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
+          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
+          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Branding (macOS)</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
+          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
+          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Branding (macOS/Win)</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
+          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
+          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>build_mac.sh / package_mac.sh</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
+          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
+          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
         </is>
       </c>
     </row>
@@ -1081,17 +1099,17 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Build (macOS)</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
@@ -1108,22 +1126,22 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>patches</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
@@ -1140,98 +1158,98 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc8 → rc9</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1246,115 +1264,115 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1369,24 +1387,24 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -1396,29 +1414,29 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1428,29 +1446,29 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -1460,29 +1478,29 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1492,29 +1510,29 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -1524,29 +1542,29 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1556,66 +1574,66 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -1625,29 +1643,29 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -1662,19 +1680,19 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -1684,29 +1702,29 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -1716,29 +1734,29 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1758,19 +1776,19 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -1780,29 +1798,29 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1812,29 +1830,29 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -1844,29 +1862,29 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -1876,29 +1894,29 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -1908,29 +1926,29 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -1940,29 +1958,29 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -1972,22 +1990,22 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -2004,29 +2022,29 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -2036,29 +2054,29 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2068,29 +2086,29 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -2100,22 +2118,22 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -2132,20 +2150,116 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>최신 버전 1.5.3 (2026-08-20) · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
+          <t>최신 버전 1.5.2 · 대상 장비: Cubicon xCeler-Plus / xCeler-I / xCeler-Mini</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.3-rc1</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.3-rc1</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.3-rc1</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.2 → 1.5.3 (다음 개발 사이클 시작)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>v1.5.2 GitHub 릴리스 발행 완료에 따라 1.5.3-rc1 로 전환.</t>
+          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
         </is>
       </c>
     </row>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -651,7 +651,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
@@ -672,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -732,7 +731,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -752,19 +751,19 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
+          <t>rc3 보완: 시험용 필라멘트(Rainbow PLA HS · TPU-HS)가 test 빌드에서도 목록에 안 뜨던 문제 방지</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
+          <t>rc3 에서 default_materials 를 정정하면서 검증 완료 9종만 넣었는데, Preset::set_visible_from_appconfig 는 [filaments] 섹션이 생기는 순간 "섹션에 없는 모든 필라멘트"를 비표시로 바꾸므로 test 빌드에서도 시험용 필라멘트가 사라졌을 것. 두 종을 default_materials 끝에 추가(기기당 9 → 11종). release 빌드에서는 prune_test_filaments 가 해당 프리셋 파일과 filament_list 항목을 지우므로 PresetBundle::load_installed_filaments 의 find_preset() 이 nullptr 을 돌려주고 "if (filament &amp;&amp; filament-&gt;is_system)" 에서 조용히 건너뜀 — 오류 없이 release 에서는 계속 제외됨(검증 완료: test 11/11 해석, release 9/11 해석). 따라서 prune 스크립트 수정 불필요.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -779,24 +778,24 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
+          <t>Cubicon TPU-HS: 현행 유지 확인 (eSUN eTPU-HS 물성표 대조)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
+          <t>요청 확인 결과 TPU-HS 는 1.5.0-rc1 에서 이미 3기종 + @base 로 추가되어 있고 test_only_filaments.txt 에도 등재되어 test 빌드 전용으로 동작 중. eSUN eTPU-HS(TPU-95A) 물성표와 대조: 밀도 1.21 g/cm³ · 노즐 온도 범위 220~250 ℃ 가 기존 프로파일 값과 일치하여 변경 없음. 자료: cubicon/profile/TPU HS Filament/물성 수치 비교표.png. 캘리브레이션(최대 체적속도 5 · PA 0.03)은 미검증 상태 유지.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -816,56 +815,56 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
+          <t>시험용 필라멘트 표시 보완 반영.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
+          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
+          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -875,29 +874,29 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
+          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
+          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -912,19 +911,19 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
+          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -934,7 +933,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -944,19 +943,19 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
+          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
+          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -966,29 +965,29 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
+          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
+          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -998,22 +997,22 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
+          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1029,22 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
+          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
+          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
         </is>
       </c>
     </row>
@@ -1062,118 +1061,118 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
+          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
+          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Branding (macOS)</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
+          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
+          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Branding (macOS/Win)</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
+          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
+          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>build_mac.sh / package_mac.sh</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
+          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
+          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
         </is>
       </c>
     </row>
@@ -1195,17 +1194,17 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Build (macOS)</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
@@ -1222,22 +1221,22 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>patches</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
@@ -1254,98 +1253,98 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc8 → rc9</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1360,115 +1359,115 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -1483,24 +1482,24 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1510,29 +1509,29 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -1542,29 +1541,29 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1574,29 +1573,29 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -1606,29 +1605,29 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1638,29 +1637,29 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -1670,66 +1669,66 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -1739,29 +1738,29 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -1776,19 +1775,19 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -1798,29 +1797,29 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1830,29 +1829,29 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -1872,19 +1871,19 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -1894,29 +1893,29 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -1926,29 +1925,29 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -1958,29 +1957,29 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -1990,29 +1989,29 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2022,29 +2021,29 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -2054,29 +2053,29 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2086,22 +2085,22 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -2118,29 +2117,29 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2150,29 +2149,29 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
@@ -2182,29 +2181,29 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -2214,22 +2213,22 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -2246,20 +2245,116 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>필라멘트 선택 목록이 비거나 Cubicon 필라멘트 대신 Default Filament 로 선택되던 문제 수정</t>
+          <t>필라멘트 선택 목록이 비거나 Cubicon 필라멘트 대신 Default Filament 로 선택되던 문제 수정 (복사한 프린터 설정 사용 시 포함)</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc4</t>
+          <t>1.5.2-rc5</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -746,24 +746,24 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>Preset loading</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>rc3 보완: 시험용 필라멘트(Rainbow PLA HS · TPU-HS)가 test 빌드에서도 목록에 안 뜨던 문제 방지</t>
+          <t>복사한 프린터 프리셋 선택 시 필라멘트 목록이 비고 Default Filament 로 선택되는 문제 수정 (patch 0011 신규)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>rc3 에서 default_materials 를 정정하면서 검증 완료 9종만 넣었는데, Preset::set_visible_from_appconfig 는 [filaments] 섹션이 생기는 순간 "섹션에 없는 모든 필라멘트"를 비표시로 바꾸므로 test 빌드에서도 시험용 필라멘트가 사라졌을 것. 두 종을 default_materials 끝에 추가(기기당 9 → 11종). release 빌드에서는 prune_test_filaments 가 해당 프리셋 파일과 filament_list 항목을 지우므로 PresetBundle::load_installed_filaments 의 find_preset() 이 nullptr 을 돌려주고 "if (filament &amp;&amp; filament-&gt;is_system)" 에서 조용히 건너뜀 — 오류 없이 release 에서는 계속 제외됨(검증 완료: test 11/11 해석, release 9/11 해석). 따라서 prune 스크립트 수정 불필요.</t>
+          <t>재발 원인은 rc3 에서 고친 default_materials 와 별개. 고객 PC 의 사용자 프린터 프리셋 "Cubicon xCeler-Plus 0.4 nozzle - 복사" 가 inherits 가 빈 문자열인 detached 상태(전체 설정 164키를 자체 보유, version 2.3.2.0 → 1.4.1 시절 생성분이 마이그레이션에서 링크 유실). Cubicon 필라멘트·프로세스는 compatible_printers 에 시스템 프리셋 이름만 나열하므로 이름이 다른 사용자 프리셋은 is_compatible_with_printer() 에서 탈락하고, 유일한 대안 경로인 is_compatible_with_parent_printer() 는 inherits() 를 비교하는데 그 값이 비어 있어 실패 → Cubicon 필라멘트 전부 비호환 → 목록 공백 + Default Filament 폴백. 고객 로그로 확정: "active printer …- 복사 / type filament, previous selected 89 becomes uncompatible / select Default Filament", 반면 시스템 프리셋 선택 시에는 정상 선택됨. 수정: PresetBundle::repair_detached_user_printers() 를 load_installed_printers 앞에 추가해, inherits 가 빈 사용자 프린터 프리셋을 printer_model + printer_variant 로 시스템 부모를 찾아 재연결. inherits 가 비어 있는 (=현재 이미 고장난) 프리셋만 건드리므로 기존 동작에는 영향 없음. 부모를 못 찾으면 순수 커스텀 프린터로 보고 그대로 둠.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc4</t>
+          <t>1.5.2-rc5</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -778,24 +778,24 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Diagnosis</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Cubicon TPU-HS: 현행 유지 확인 (eSUN eTPU-HS 물성표 대조)</t>
+          <t>rc3 default_materials 수정은 정상 동작 확인</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>요청 확인 결과 TPU-HS 는 1.5.0-rc1 에서 이미 3기종 + @base 로 추가되어 있고 test_only_filaments.txt 에도 등재되어 test 빌드 전용으로 동작 중. eSUN eTPU-HS(TPU-95A) 물성표와 대조: 밀도 1.21 g/cm³ · 노즐 온도 범위 220~250 ℃ 가 기존 프로파일 값과 일치하여 변경 없음. 자료: cubicon/profile/TPU HS Filament/물성 수치 비교표.png. 캘리브레이션(최대 체적속도 5 · PA 0.03)은 미검증 상태 유지.</t>
+          <t>고객 PC 의 OrcaForCubicon.conf 에 [filaments] 33종(11필라멘트 × 3기종)이 정상 기록되어 있고 로그에도 "printer … already has default filament …" 로 남아 rc3·rc4 수정은 의도대로 동작 중. 이번 재발은 동일 증상의 다른 원인이었음. 자료: .problem/20260820_필라멘트 창 이름 없어짐/OrcaForCubicon.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc4</t>
+          <t>1.5.2-rc5</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -815,19 +815,19 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>시험용 필라멘트 표시 보완 반영.</t>
+          <t>복사 프린터 프리셋 호환성 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
+          <t>rc3 보완: 시험용 필라멘트(Rainbow PLA HS · TPU-HS)가 test 빌드에서도 목록에 안 뜨던 문제 방지</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
+          <t>rc3 에서 default_materials 를 정정하면서 검증 완료 9종만 넣었는데, Preset::set_visible_from_appconfig 는 [filaments] 섹션이 생기는 순간 "섹션에 없는 모든 필라멘트"를 비표시로 바꾸므로 test 빌드에서도 시험용 필라멘트가 사라졌을 것. 두 종을 default_materials 끝에 추가(기기당 9 → 11종). release 빌드에서는 prune_test_filaments 가 해당 프리셋 파일과 filament_list 항목을 지우므로 PresetBundle::load_installed_filaments 의 find_preset() 이 nullptr 을 돌려주고 "if (filament &amp;&amp; filament-&gt;is_system)" 에서 조용히 건너뜀 — 오류 없이 release 에서는 계속 제외됨(검증 완료: test 11/11 해석, release 9/11 해석). 따라서 prune 스크립트 수정 불필요.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -874,24 +874,24 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
+          <t>Cubicon TPU-HS: 현행 유지 확인 (eSUN eTPU-HS 물성표 대조)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
+          <t>요청 확인 결과 TPU-HS 는 1.5.0-rc1 에서 이미 3기종 + @base 로 추가되어 있고 test_only_filaments.txt 에도 등재되어 test 빌드 전용으로 동작 중. eSUN eTPU-HS(TPU-95A) 물성표와 대조: 밀도 1.21 g/cm³ · 노즐 온도 범위 220~250 ℃ 가 기존 프로파일 값과 일치하여 변경 없음. 자료: cubicon/profile/TPU HS Filament/물성 수치 비교표.png. 캘리브레이션(최대 체적속도 5 · PA 0.03)은 미검증 상태 유지.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -911,56 +911,56 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
+          <t>시험용 필라멘트 표시 보완 반영.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
+          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
+          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -970,29 +970,29 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
+          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
+          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1007,19 +1007,19 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
+          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1039,19 +1039,19 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
+          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
+          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1061,29 +1061,29 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
+          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
+          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -1093,22 +1093,22 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
+          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
         </is>
       </c>
     </row>
@@ -1125,22 +1125,22 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
+          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
+          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
         </is>
       </c>
     </row>
@@ -1157,118 +1157,118 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
+          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
+          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Branding (macOS)</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
+          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
+          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Branding (macOS/Win)</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
+          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
+          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>build_mac.sh / package_mac.sh</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
+          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
+          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Build (macOS)</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
@@ -1317,22 +1317,22 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>patches</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
@@ -1349,98 +1349,98 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc8 → rc9</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1455,115 +1455,115 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -1605,29 +1605,29 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1637,29 +1637,29 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -1669,29 +1669,29 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -1701,29 +1701,29 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -1733,29 +1733,29 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1765,66 +1765,66 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -1834,29 +1834,29 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -1871,19 +1871,19 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -1893,29 +1893,29 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -1925,29 +1925,29 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -1967,19 +1967,19 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -1989,29 +1989,29 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2021,29 +2021,29 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -2053,29 +2053,29 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -2117,29 +2117,29 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2149,29 +2149,29 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -2213,29 +2213,29 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
@@ -2245,29 +2245,29 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -2277,29 +2277,29 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
@@ -2309,22 +2309,22 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -2341,20 +2341,116 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
           <t>Chore</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>

--- a/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
+++ b/cubicon/doc/OrcaForCubicon_ReleaseNotes.xlsx
@@ -671,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -731,44 +731,44 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc5</t>
+          <t>1.5.3-rc0</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Preset loading</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>복사한 프린터 프리셋 선택 시 필라멘트 목록이 비고 Default Filament 로 선택되는 문제 수정 (patch 0011 신규)</t>
+          <t>기종별 출력 제한 — G-code 에 요구 조형 크기 전달 (슬라이서 쪽 선반영)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>재발 원인은 rc3 에서 고친 default_materials 와 별개. 고객 PC 의 사용자 프린터 프리셋 "Cubicon xCeler-Plus 0.4 nozzle - 복사" 가 inherits 가 빈 문자열인 detached 상태(전체 설정 164키를 자체 보유, version 2.3.2.0 → 1.4.1 시절 생성분이 마이그레이션에서 링크 유실). Cubicon 필라멘트·프로세스는 compatible_printers 에 시스템 프리셋 이름만 나열하므로 이름이 다른 사용자 프리셋은 is_compatible_with_printer() 에서 탈락하고, 유일한 대안 경로인 is_compatible_with_parent_printer() 는 inherits() 를 비교하는데 그 값이 비어 있어 실패 → Cubicon 필라멘트 전부 비호환 → 목록 공백 + Default Filament 폴백. 고객 로그로 확정: "active printer …- 복사 / type filament, previous selected 89 becomes uncompatible / select Default Filament", 반면 시스템 프리셋 선택 시에는 정상 선택됨. 수정: PresetBundle::repair_detached_user_printers() 를 load_installed_printers 앞에 추가해, inherits 가 빈 사용자 프린터 프리셋을 printer_model + printer_variant 로 시스템 부모를 찾아 재연결. inherits 가 비어 있는 (=현재 이미 고장난) 프리셋만 건드리므로 기존 동작에는 영향 없음. 부모를 못 찾으면 순수 커스텀 프린터로 보고 그대로 둠.</t>
+          <t>슬라이싱한 기종보다 작은 프린터에서 출력되지 않도록, 3기종의 machine_start_gcode 에 REQ_X={print_bed_size[0]} REQ_Y={print_bed_size[1]} REQ_Z={printable_height} 파라미터 추가. 조형 공간이 Mini(150³) ⊂ xCeler-I(250×250×290) ⊂ Plus(310³) 로 완전 포함 관계라 크기 비교만으로 "Mini 파일=전 기종 / I 파일=I·Plus / Plus 파일=Plus" 규칙이 성립하며, 기종 추가 시 규칙 수정 불필요. print_bed_size 는 GCode.cpp:2911 에서 설정되고 시작 G-code 는 3118 에서 처리되므로 순서상 사용 가능(코드 수정 불필요). ★ 실제 차단은 프린터의 Klipper START_PRINT 매크로에서 REQ_* 와 printer.toolhead.axis_maximum 을 비교해 action_raise_error() 를 호출해야 완성됨 — 펌웨어 미반영 상태에서는 파라미터가 무시되어 동작 변화 없음. 기존 슬라이싱 파일도 파라미터가 없으면 매크로에서 default(0) 으로 허용되도록 구현할 것(기본값=허용).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc5</t>
+          <t>1.5.3-rc0</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -778,29 +778,29 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Diagnosis</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>rc3 default_materials 수정은 정상 동작 확인</t>
+          <t>프로파일 패키지 버전 02.03.05.00 → 02.03.06.00</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>고객 PC 의 OrcaForCubicon.conf 에 [filaments] 33종(11필라멘트 × 3기종)이 정상 기록되어 있고 로그에도 "printer … already has default filament …" 로 남아 rc3·rc4 수정은 의도대로 동작 중. 이번 재발은 동일 증상의 다른 원인이었음. 자료: .problem/20260820_필라멘트 창 이름 없어짐/OrcaForCubicon.</t>
+          <t>Cubicon.json. 변경된 machine_start_gcode 를 기설치 사용자에게 전파.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc5</t>
+          <t>1.5.3-rc0</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -815,19 +815,19 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>기본 버전 1.5.2 → 1.5.3 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>복사 프린터 프리셋 호환성 수정 반영.</t>
+          <t>1.5.2-rc5 → 1.5.3-rc0. v1.5.2 배포 완료에 따라 사이클 전환.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc4</t>
+          <t>1.5.2-rc5</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -842,24 +842,24 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>Preset loading</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>rc3 보완: 시험용 필라멘트(Rainbow PLA HS · TPU-HS)가 test 빌드에서도 목록에 안 뜨던 문제 방지</t>
+          <t>복사한 프린터 프리셋 선택 시 필라멘트 목록이 비고 Default Filament 로 선택되는 문제 수정 (patch 0011 신규)</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>rc3 에서 default_materials 를 정정하면서 검증 완료 9종만 넣었는데, Preset::set_visible_from_appconfig 는 [filaments] 섹션이 생기는 순간 "섹션에 없는 모든 필라멘트"를 비표시로 바꾸므로 test 빌드에서도 시험용 필라멘트가 사라졌을 것. 두 종을 default_materials 끝에 추가(기기당 9 → 11종). release 빌드에서는 prune_test_filaments 가 해당 프리셋 파일과 filament_list 항목을 지우므로 PresetBundle::load_installed_filaments 의 find_preset() 이 nullptr 을 돌려주고 "if (filament &amp;&amp; filament-&gt;is_system)" 에서 조용히 건너뜀 — 오류 없이 release 에서는 계속 제외됨(검증 완료: test 11/11 해석, release 9/11 해석). 따라서 prune 스크립트 수정 불필요.</t>
+          <t>재발 원인은 rc3 에서 고친 default_materials 와 별개. 고객 PC 의 사용자 프린터 프리셋 "Cubicon xCeler-Plus 0.4 nozzle - 복사" 가 inherits 가 빈 문자열인 detached 상태(전체 설정 164키를 자체 보유, version 2.3.2.0 → 1.4.1 시절 생성분이 마이그레이션에서 링크 유실). Cubicon 필라멘트·프로세스는 compatible_printers 에 시스템 프리셋 이름만 나열하므로 이름이 다른 사용자 프리셋은 is_compatible_with_printer() 에서 탈락하고, 유일한 대안 경로인 is_compatible_with_parent_printer() 는 inherits() 를 비교하는데 그 값이 비어 있어 실패 → Cubicon 필라멘트 전부 비호환 → 목록 공백 + Default Filament 폴백. 고객 로그로 확정: "active printer …- 복사 / type filament, previous selected 89 becomes uncompatible / select Default Filament", 반면 시스템 프리셋 선택 시에는 정상 선택됨. 수정: PresetBundle::repair_detached_user_printers() 를 load_installed_printers 앞에 추가해, inherits 가 빈 사용자 프린터 프리셋을 printer_model + printer_variant 로 시스템 부모를 찾아 재연결. inherits 가 비어 있는 (=현재 이미 고장난) 프리셋만 건드리므로 기존 동작에는 영향 없음. 부모를 못 찾으면 순수 커스텀 프린터로 보고 그대로 둠.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc4</t>
+          <t>1.5.2-rc5</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -874,24 +874,24 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Diagnosis</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Cubicon TPU-HS: 현행 유지 확인 (eSUN eTPU-HS 물성표 대조)</t>
+          <t>rc3 default_materials 수정은 정상 동작 확인</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>요청 확인 결과 TPU-HS 는 1.5.0-rc1 에서 이미 3기종 + @base 로 추가되어 있고 test_only_filaments.txt 에도 등재되어 test 빌드 전용으로 동작 중. eSUN eTPU-HS(TPU-95A) 물성표와 대조: 밀도 1.21 g/cm³ · 노즐 온도 범위 220~250 ℃ 가 기존 프로파일 값과 일치하여 변경 없음. 자료: cubicon/profile/TPU HS Filament/물성 수치 비교표.png. 캘리브레이션(최대 체적속도 5 · PA 0.03)은 미검증 상태 유지.</t>
+          <t>고객 PC 의 OrcaForCubicon.conf 에 [filaments] 33종(11필라멘트 × 3기종)이 정상 기록되어 있고 로그에도 "printer … already has default filament …" 로 남아 rc3·rc4 수정은 의도대로 동작 중. 이번 재발은 동일 증상의 다른 원인이었음. 자료: .problem/20260820_필라멘트 창 이름 없어짐/OrcaForCubicon.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc4</t>
+          <t>1.5.2-rc5</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -911,19 +911,19 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>시험용 필라멘트 표시 보완 반영.</t>
+          <t>복사 프린터 프리셋 호환성 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -943,19 +943,19 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
+          <t>rc3 보완: 시험용 필라멘트(Rainbow PLA HS · TPU-HS)가 test 빌드에서도 목록에 안 뜨던 문제 방지</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
+          <t>rc3 에서 default_materials 를 정정하면서 검증 완료 9종만 넣었는데, Preset::set_visible_from_appconfig 는 [filaments] 섹션이 생기는 순간 "섹션에 없는 모든 필라멘트"를 비표시로 바꾸므로 test 빌드에서도 시험용 필라멘트가 사라졌을 것. 두 종을 default_materials 끝에 추가(기기당 9 → 11종). release 빌드에서는 prune_test_filaments 가 해당 프리셋 파일과 filament_list 항목을 지우므로 PresetBundle::load_installed_filaments 의 find_preset() 이 nullptr 을 돌려주고 "if (filament &amp;&amp; filament-&gt;is_system)" 에서 조용히 건너뜀 — 오류 없이 release 에서는 계속 제외됨(검증 완료: test 11/11 해석, release 9/11 해석). 따라서 prune 스크립트 수정 불필요.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -970,24 +970,24 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
+          <t>Cubicon TPU-HS: 현행 유지 확인 (eSUN eTPU-HS 물성표 대조)</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
+          <t>요청 확인 결과 TPU-HS 는 1.5.0-rc1 에서 이미 3기종 + @base 로 추가되어 있고 test_only_filaments.txt 에도 등재되어 test 빌드 전용으로 동작 중. eSUN eTPU-HS(TPU-95A) 물성표와 대조: 밀도 1.21 g/cm³ · 노즐 온도 범위 220~250 ℃ 가 기존 프로파일 값과 일치하여 변경 없음. 자료: cubicon/profile/TPU HS Filament/물성 수치 비교표.png. 캘리브레이션(최대 체적속도 5 · PA 0.03)은 미검증 상태 유지.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc3</t>
+          <t>1.5.2-rc4</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1007,56 +1007,56 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
+          <t>시험용 필라멘트 표시 보완 반영.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Machine profile</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
+          <t>필라멘트 목록이 비거나 Default Filament 로 선택되는 문제 수정</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
+          <t>기기 모델 3종의 default_materials 가 실제 프리셋 이름과 달랐음 — "Cubicon PLA @Cubicon xCeler-Plus" 로 적혀 있으나 실제 이름은 "… 0.4 nozzle" 까지 포함. PresetBundle::load_installed_filaments 는 이 문자열로 filaments.find_preset() 을 호출하므로 항상 nullptr → OrcaSlicer.conf 의 [filaments] 섹션에 Cubicon 필라멘트가 한 번도 기록되지 않음. Preset::set_visible_from_appconfig 는 [filaments] 섹션이 "존재할 때만" 표시 여부를 덮어쓰므로, 설정 마법사나 필라멘트 목록 편집 등으로 이 섹션이 처음 생기는 순간 섹션에 없는 모든 필라멘트가 비표시로 바뀜 → 선택 중이던 Cubicon 필라멘트 이름이 사라지고 Default Filament 로 폴백(증상 1·2 동일 원인). 3개 기기 모델의 default_materials 를 실제 프리셋 이름 9종(PLA · PLA+ · PLAi21 · PETG · ABS · ABS-A100 · ABSk · PC · PA-CF)으로 정정. 이미 깨진 설정도 다음 실행 시 load_installed_filaments 가 섹션을 다시 채워 자동 복구됨. 시험용 필라멘트(Rainbow PLA HS · TPU-HS)는 release 빌드에서 제외되므로 목록에 넣지 않음.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1066,29 +1066,29 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
+          <t>프로파일 패키지 버전 02.03.04.00 → 02.03.05.00</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
+          <t>Cubicon.json. 수정된 기기 모델 파일을 기설치 사용자에게 전파하기 위해 상승.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc2</t>
+          <t>1.5.2-rc3</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -1103,19 +1103,19 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
+          <t>v1.5.2 발행 이후의 수정이지만 버전 번호는 1.5.2 를 유지하고 rc 만 상승. release 빌드가 rc 접미사를 제거하므로 앱 표시 버전은 1.5.2 그대로.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
+          <t>rc1 조정: 인필 밀도는 15 % 유지 (패턴만 zigzag)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
+          <t>cubicon common @base: sparse_infill_density 20 → 15 로 되돌림. 패턴 변경만으로도 방향별 선간격이 6.0 mm(grid 15 %) → 3.0 mm(zigzag 15 %) 로 절반이 되므로 상면 지지는 이미 개선되며, 밀도를 올리지 않아 인필 시간·재료 증가가 없음. sparse_infill_pattern = zigzag 는 그대로 유지.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -1157,29 +1157,29 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
+          <t>rc1 조정: 최대 체적속도 21 mm³/s 적용 범위를 PLAi21 로 한정</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
+          <t>Cubicon PLA @base 는 23 으로 복귀하고, Cubicon PLAi21 @base 에 filament_max_volumetric_speed 21 을 직접 지정. rc1 은 PLA @base 를 21 로 낮춰 Cubicon PLA 까지 함께 내려갔으나, 21 은 PLAi21 에만 해당하는 값. PLA+ 는 8 이 정상값으로 확인되어 그대로 유지. PA 기본값(enable_pressure_advance 1 / pressure_advance 0.025)은 rc1 대로 PLA @base 에 유지 — PLA · PLAi21 에 적용되고 PLA+(0.025) · Rainbow PLA HS(0.03) 는 자체 값 사용.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>1.5.2-rc1</t>
+          <t>1.5.2-rc2</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1189,22 +1189,22 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
+          <t>인필 밀도 원복 및 체적속도 적용 범위 조정 반영. 프로파일 패키지 02.03.04.00 은 미배포 상태라 유지.</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Profile package</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
+          <t>스파스 인필 패턴 grid → zigzag, 밀도 15 → 20 %</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
+          <t>cubicon common @base (전 재료·전 장비 공통). grid 는 한 층 안에서 0°/90° 두 방향을 모두 깔기 때문에 교차점이 이중 압출되고, 노즐이 그 돌기를 다시 지나가며 소음·간섭·출력 실패를 유발함 (FillGrid::fill_surface 가 {0, PI/2} 두 sweep 을 한 번에 채움 — 소스 확인). zigzag(FillZigZag)는 층당 한 방향만 깔아 자기 교차가 없음. 또한 grid 는 방향 수만큼 밀도를 나누므로(density /= sweep 수) 15 % grid 의 방향별 선간격은 6.0 mm 였고, 20 % zigzag 는 2.25 mm 로 상면 지지가 오히려 촘촘해짐. 인필 소요 시간·재료는 15 % 대비 약 33 % 증가.</t>
         </is>
       </c>
     </row>
@@ -1253,118 +1253,118 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
+          <t>소형 둘레 감속 활성화: 임계값 0 → 6.5 mm, 속도 50 % → 30 mm/s 절대값</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
+          <t>임계값 0 은 “자동”이 아니라 기능 완전 비활성 — 판정식이 loop.length() &lt;= 2*PI*임계값 이라 0 이면 어떤 루프도 걸리지 않음 (GCode.cpp:5809 + libslic3r.h:84 SMALL_PERIMETER_LENGTH). 6.5 mm 는 이 값이 설정으로 노출되기 전 하드코딩 상수와 동일하며, 루프 길이 40.8 mm(원 지름 13 mm / 정사각형 한 변 10.2 mm) 이하를 소형으로 판정. 속도도 함께 절대값으로 바꾼 이유: 50 % 는 outer_wall_speed(200) 기준이라 100 mm/s 인데, 체적 상한 때문에 외벽 실제 속도가 이미 107 mm/s 라 감속 폭이 7 mm/s 에 불과했음. 경성콘크리트 고객 소형 파이프(⌀4.6 외경 14.3 mm · ⌀2.4 내경 7.5 mm) 대응.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Branding (macOS)</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
+          <t>PLA 기본에 Pressure Advance 기본값 부여, 최대 체적속도 23 → 21 mm³/s</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
+          <t>Cubicon PLA @base: enable_pressure_advance 1, pressure_advance 0.025 신규 지정, filament_max_volumetric_speed 23 → 21. 적용 범위 = Cubicon PLA(3기종) + Cubicon PLAi21(오버라이드 없음). Cubicon PLA+ @base(8 mm³/s, PA 0.025)와 Rainbow PLA HS @base(17, PA 0.03)는 자체 값을 유지하므로 변동 없음.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Branding (macOS/Win)</t>
+          <t>Profile package</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
+          <t>프로파일 패키지 버전 02.03.03.00 → 02.03.04.00</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
+          <t>Cubicon.json. 인필 패턴·소형 둘레·PLA PA 변경을 기설치 사용자에게 전파하기 위해 패키지 버전 상승.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc9</t>
+          <t>1.5.2-rc1</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>build_mac.sh / package_mac.sh</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
+          <t>기본 버전 1.5.1 → 1.5.2 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
+          <t>1.5.1-rc9 → 1.5.2-rc1. 프로파일 변경 3건 반영.</t>
         </is>
       </c>
     </row>
@@ -1386,17 +1386,17 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Build (macOS)</t>
+          <t>Branding (macOS)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
+          <t>실행 중 Dock 아이콘이 기본 Orca 로 되돌아가던 문제 수정</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
+          <t>MainFrame.cpp 의 __APPLE__ 블록이 OrcaSlicerTaskBarIcon(wxTBI_DOCK) 의 아이콘을 resources/images/OrcaSlicer-mac_256px.ico 로 직접 지정하는데 이 파일이 Cubicon 오버레이에 없었음 — Icon.icns/128px.png 는 Finder/Launchpad·윈도우 아이콘만 담당. 런치 바운스 직후 기본 Orca 아이콘으로 복귀하던 원인. 동일 결합 마크로 오버레이에 추가.</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>patches</t>
+          <t>Branding (macOS/Win)</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
+          <t>Cubicon + Orca 결합 앱 아이콘 적용 (macOS Dock/Finder · Windows exe)</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
+          <t>앱 아이콘이 양 플랫폼 모두 실제로는 리브랜딩되지 않은 상태였음: resources/Icon.icns 가 오버레이에 없었고, exe 에 컴파일되는 resources/images/OrcaSlicer.ico 는 업스트림과 바이트 동일. 디자인 = Cubicon "C" 마크를 주형상 + OrcaSlicer 고래 마크(배경 투명화)를 약 1/2 크기 배지. 추가/갱신: Icon.icns(신규, MACOSX_BUNDLE_ICON_FILE), OrcaSlicer.ico(Windows exe), OrcaSlicer_128px.png(런타임 Dock — MainFrame.cpp SetIcon), OrcaSlicer_192px.png(마법사/다이얼로그).</t>
         </is>
       </c>
     </row>
@@ -1445,98 +1445,98 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>build_mac.sh / package_mac.sh</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc8 → rc9</t>
+          <t>macOS 빌드에 test/release 유형 추가 · DMG 출력 경로 정리</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
+          <t>build_win.ps1 의 -BuildType 을 macOS 에 대응(-b test|release, 기본 test). release 는 cubicon_version.txt 의 -rc 접미사를 빌드 동안만 제거(종료 시 항상 복원)하고, 미검증 test-only 필라멘트를 prune_test_filaments.sh(ps1 의 bash+jq 포팅)로 제외. package_mac.sh 기본 DMG 출력 dist/ → installer/macos/ (Windows 패키지 배치와 일치), .gitignore 에 installer/macos/*.dmg 추가.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>GitHub Release</t>
+          <t>Build (macOS)</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
+          <t>Xcode 제너레이터 / GMP SDK 설정 및 SDK26 경고 오탐 대응</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
+          <t>build_mac.sh: Command Line Tools 만 선택된 환경이면 활성 developer dir 을 Xcode.app 으로 전환(CMake Xcode 제너레이터가 xcodebuild 를 호출하므로 필수), SDKROOT export 로 -isysroot 없이 cc 를 호출하는 autoconf 계열 deps(GMP 등)가 libSystem 을 찾게 함. CMakeLists.txt(patch 0010): macOS 26 SDK + 11.3 배포 타깃에서 Cocoa/AppKit/CoreGraphics 헤더 include 만으로 발생하는 -Wunguarded-availability-new 오탐을 -Wno-error= 로 강등(하위 그룹이라 -Werror=unguarded-availability 만으로는 계속 치명적). 실제 코드 사용을 잡는 non-"-new" 변형은 fatal 유지.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>patches</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
+          <t>중복 패치 번호 정리: 0008-macos-… → 0010-macos-…</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
+          <t>macOS SDK26 패치가 0008-gcode-header-… 와 번호 중복. apply_overlay 는 파일명 정렬 순서로 적용하므로 동작상 문제는 없었으나 번호 충돌을 제거. 10개 패치가 pristine HEAD 트리에 순차 clean 적용됨을 확인.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc8</t>
+          <t>1.5.1-rc9</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -1551,115 +1551,115 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc7 → rc8</t>
+          <t>제품 버전 rc8 → rc9</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>스플래시 로고/제품명 표시 변경 반영.</t>
+          <t>macOS 빌드/아이콘 수정 반영. cubicon_version.txt 의 UTF-8 BOM 제거 — release 빌드의 Set-Content -Encoding utf8 이 남긴 것으로, CMake file(STRINGS) 와 PowerShell 모두 BOM 을 걸러내므로 버전 파싱에는 영향 없음(확인).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>GitHub Release</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
+          <t>v1.5.1 정식 빌드 배포 (릴리스 자산 교체)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
+          <t>기존 v1.5.1 릴리스(2026-07-30 발행)의 07-31 exe 를 08-11 정식 빌드 "OrcaForCubicon Setup V1.5.1_20260811_104910.exe" 로 교체하고 Latest 유지. rc2~rc8 변경이 모두 포함된 빌드. 태그 v1.5.1 을 rc8 커밋으로 이동. 앱 표시 버전이 1.5.1 이므로 기존 1.5.1 사용자에게는 업데이트 팝업이 뜨지 않음.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc7</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc6 → rc7</t>
+          <t>스플래시에 CUBICON · Orca 두 로고 동시 표시 + 제품명 추가</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>서포트/라프트 기본값 조정.</t>
+          <t>patch 0005. 1.4.x 처럼 두 브랜드 로고를 "CUBICON x Orca Slicer" 한 줄로 표시 (양쪽 모두 워드마크 포함, 두 로고+간격이 스플래시 폭의 86%). Orca 는 기존 리소스 OrcaSlicer_horizontal_light/dark.svg 를 BitmapCache::load_svg 로 로드(dark_mode 전달, HiDPI 비트맵은 논리 크기로 재정규화하여 macOS 레이아웃 어긋남 방지). 로고 행 아래에 제품명(SLIC3R_APP_FULL_NAME = "OrcaForCubicon")을 Head_24×1.35 · #009688 로 추가. Orca 로고 로드 실패 시 기존처럼 CUBICON 로고만 표시(회귀 없음).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc8</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
+          <t>제품 버전 rc7 → rc8</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
+          <t>스플래시 로고/제품명 표시 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc6</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc5 → rc6</t>
+          <t>서포트 기본 off · 라프트 레이어 0 으로 조정</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>서포트 옵션 변경 반영.</t>
+          <t>cubicon common @base: enable_support 1→0, raft_layers 3→0. rc6 의 서포트/라프트 나머지 변경(빌드플레이트 off, 임계각 30, tree(auto), 접점 0.2, 오버행 벽 감지 on)은 유지.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc7</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -1701,29 +1701,29 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
+          <t>제품 버전 rc6 → rc7</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
+          <t>서포트/라프트 기본값 조정.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc5</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -1733,29 +1733,29 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>서포트·라프트·오버행 기본값 변경 (기본 프로세스, 전 재료 공통)</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>빌드 스크립트 패치충돌 수정 반영.</t>
+          <t>cubicon common @base: 서포트 사용 off→on, 빌드플레이트에만 on→off, 임계각 15→30, 유형 normal(auto)→tree(auto), 라프트 접점 Z 0.1→0.2, 라프트 레이어 0→3, 오버행 벽 감지 off→on.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc6</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1765,29 +1765,29 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Process profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
+          <t>제품 버전 rc5 → rc6</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
+          <t>서포트 옵션 변경 반영.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc4</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -1797,29 +1797,29 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>빌드 시 patch 0008 충돌(U src/libslic3r/utils.cpp) 수정</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>정밀도 공차 프로세스 반영.</t>
+          <t>build_win.ps1 이 소스를 인덱스로 리셋('git checkout -- src')해, git apply --3way 가 staged 로 남긴 옛 패치본이 새 패치와 충돌하던 문제. 'git checkout HEAD -- ...'(인덱스+워크트리 모두 HEAD로 리셋)로 변경해 매 빌드 pristine 보장.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc5</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1829,29 +1829,29 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
+          <t>빌드 스크립트 패치충돌 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc3</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -1861,66 +1861,66 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Process profile</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>정밀도(공차) 보정 기본 프로세스 반영 (전 재료 공통)</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
+          <t>cubicon common @base: 코끼리발 보정 0.15→0.2 · 보정 레이어 2 · X-Y 구멍 보정 0.2 · X-Y 윤곽 보상 0.02 추가. resolution 0.012 · slice_closing 0.049 · EF density 100% · 정밀한 벽/정확한 Z · 원호맞춤 off 는 기존 일치. Rainbow PLA HS 공차 캘리브레이션 결과이며 공정 설정이라 전 재료에 공통 적용됨.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc4</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>G-code load</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
+          <t>정밀도 공차 프로세스 반영.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -1930,29 +1930,29 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Installer / Runtime</t>
+          <t>Filament profile</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
+          <t>Rainbow PLA HS 캘리브레이션 확정값 반영</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
+          <t>Cubicon Rainbow PLA HS @base: 최대 체적 속도 28→17 mm³/s(실측), Pressure Advance 0.03 신규 활성화. 온도(215/220)·베드(60)·유량비율(0.98)·후퇴(2mm 상속)는 캘리브레이션으로 적정 확인. 여전히 test-only. 상세: Rainbow PLA HS_ProfileUpdate_20260731_R0.pptx.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>1.5.1-rc2</t>
+          <t>1.5.1-rc3</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -1967,19 +1967,19 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
+          <t>Rainbow PLA HS 프로파일 캘리브레이션 반영.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>1.5.1-rc1</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -1989,29 +1989,29 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>version / release</t>
+          <t>G-code load</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
+          <t>OrcaForCubicon(1.4.1 등) 및 신규 1.5.0 gcode 로드 실패 수정 (patch 0008 회귀 대응)</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
+          <t>patch 0008 로 헤더를 '; generated by OrcaSlicer'로 바꾼 뒤, Config.cpp 의 로드 검증이 여전히 '; generated by OrcaForCubicon' 만 허용해 자기 파일조차 'Not a gcode file generated by OrcaForCubicon' 로 거부되던 문제. 검증에 '; generated by ' + SLIC3R_OFFICIAL_NAME('OrcaSlicer') 허용을 추가(patch 0008 갱신).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2021,29 +2021,29 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Installer / Runtime</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
+          <t>WebView2 Evergreen 런타임 조건부 설치 추가 (마법사 blank 방지)</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
+          <t>WebView2Loader.dll 만으로는 부족 — 클린 PC에 WebView2 런타임이 없으면 설정 마법사가 blank. NSIS 에서 레지스트리(EdgeUpdate pv) 확인 후 미설치 시 MicrosoftEdgeWebview2Setup.exe 를 silent 설치. package_win.ps1 이 부트스트래퍼를 자동 다운로드해 번들. (VC++ CRT/.NET-런타임 이슈는 CopyRuntime+vc_redist 로 기존에 이미 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc5</t>
+          <t>1.5.1-rc2</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -2063,19 +2063,19 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc4 → rc5</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>다크모드 스플래시 로고 수정 반영.</t>
+          <t>gcode 로드 수정 + WebView2 런타임 준비 반영.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.1-rc1</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Build / Filament</t>
+          <t>version / release</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
+          <t>기본 버전 1.5.0 → 1.5.1 (다음 개발 사이클 시작)</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
+          <t>GitHub v1.5.0 발행 후 v1.5.1 을 추가 발행하여, v1.5.0 실행 시 업데이트 알림 팝업이 정상 동작하는지 end-to-end 검증하기 위한 버전 업. release 빌드 시 '1.5.1' 로 태깅.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc4</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -2117,29 +2117,29 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc3 → rc4</t>
+          <t>다크모드 스플래시 로고에서 legacy 'style' 문구 제거</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
+          <t>splash_logo_dark.png 가 큐비콘 legacy 'style CUBICON' 로고였음(Style 시리즈는 OrcaForCubicon 미지원). light 로고 기반으로 흰색 CUBICON 텍스트 + 컬러 아이콘의 다크모드 전용 로고로 교체(2495→2125px).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc5</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2149,29 +2149,29 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Update check</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
+          <t>제품 버전 rc4 → rc5</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
+          <t>다크모드 스플래시 로고 수정 반영.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc3</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
@@ -2181,29 +2181,29 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>Build / Filament</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc2 → rc3</t>
+          <t>테스트 전용 필라멘트 분리 (test 빌드=포함 / release 빌드=제외)</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>업데이트 알림 기능 추가 반영.</t>
+          <t>cubicon/version/test_only_filaments.txt 매니페스트에 나열한 미검증 필라멘트를 release 빌드에서만 제거(cubicon/scripts/prune_test_filaments.ps1, build_win.ps1 -BuildType release 에서 호출). SSOT(cubicon/resources)는 전부 유지 → test 빌드는 모두 포함. 현재 test 전용: Cubicon Rainbow PLA HS, Cubicon TPU-HS(+fdm_filament_tpu). 검증 완료 시 매니페스트에서 해당 줄만 삭제하면 정식 승격.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc4</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -2213,29 +2213,29 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>G-code / Mainsail</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
+          <t>제품 버전 rc3 → rc4</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
+          <t>테스트/정식 필라멘트 분리 기능 반영.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
@@ -2245,29 +2245,29 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>Update check</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>release / test 빌드 유형 옵션 추가</t>
+          <t>OrcaForCubicon 전용 업데이트 알림 기능 (OrcaSlicer 기본 체크 비활성화)</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
+          <t>실행 시 GitHub 최신 릴리스(api.github.com/repos/Hyvision/OrcaForCubicon/releases/latest)를 조회해 제품버전 CUBI_ORCA_VERSION 과 비교, 새 정식 릴리스가 있으면 팝업 알림 → '다운로드' 시 브라우저로 릴리스 페이지 열기. 정식 릴리스만 대상(/releases/latest 가 draft·prerelease 자동 제외). OrcaSlicer 의 check_new_version_sf 는 시작·수동 '업데이트 확인' 메뉴 양쪽에서 check_new_version_cubicon 으로 대체. 기존 UpdateVersionDialog 재사용. (patch 0009) ※ 동작하려면 레포 public 전환 + GitHub Releases 발행 필요.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc2</t>
+          <t>1.5.0-rc3</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>build_win.ps1</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
+          <t>제품 버전 rc2 → rc3</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
+          <t>업데이트 알림 기능 추가 반영.</t>
         </is>
       </c>
     </row>
@@ -2309,29 +2309,29 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>G-code / Mainsail</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>제품 버전 rc1 → rc2</t>
+          <t>G-code 헤더 슬라이서명·버전 정정 (Moonraker 메타데이터 파싱 복원)</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
+          <t>header_slic3r_generated() 가 "OrcaForCubicon 2.4.2" → "OrcaSlicer &lt;제품버전&gt;" 로 변경. Moonraker/Mainsail 은 인식된 슬라이서명(OrcaSlicer 등)일 때만 슬라이싱 정보를 파싱함 → 기존엔 Unknown+정보 없음. 버전도 Orca 2.4.2 대신 재정의 제품버전 표기. Orca 자체 재파싱은 GCodeProcessor 의 "generated by OrcaSlicer" producer 태그로 유지. (patch 0008)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -2341,29 +2341,29 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Machine profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+          <t>release / test 빌드 유형 옵션 추가</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+          <t>-BuildType test|release (대화식 프롬프트 4번). release 는 버전의 -rc 접미사를 제거하여 splash·버전정보·About 대화상자·G-code 헤더·인스톨러명 모두에 반영. test 는 rc 유지. cubicon_version.txt(SSOT)를 빌드 중 임시 수정 후 finally 에서 원복.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
@@ -2373,29 +2373,29 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>build_win.ps1</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon TPU-HS</t>
+          <t>병렬 컴파일 잡을 메모리 기준으로도 제한 (-MemPerJobGB)</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+          <t>28코어/32GB 환경에서 CpuPercent 70%(=19잡)로 libslic3r PCH 컴파일 시 페이지파일 고갈(C3859/C1076/OS 1455) 발생. jobs = min(CPU 상한, floor((총RAM-4)/MemPerJobGB[기본3])) 로 제한하여 재발 방지.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>1.5.0-rc1</t>
+          <t>1.5.0-rc2</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -2405,22 +2405,22 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Chore</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Filament profile</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+          <t>제품 버전 rc1 → rc2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+          <t>cubicon/version/cubicon_version.txt. 규칙: 매 수정마다 rc 1 증가(반영 여부 식별용).</t>
         </is>
       </c>
     </row>
@@ -2437,20 +2437,116 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Chore</t>
+          <t>Feat</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
+          <t>Machine profile</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>장비 Max Jerk 하향 (Bambu·Creality 기조: 고가감속·저저크)</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>xCeler-Plus/I/Mini 3종: X 20→5, Y 20→5, Z 20→2, E 20→2.5 mm/s. 캔틸레버 베드 편심 틸트로 레이어 중 Z가 상시 반전할 때 높은 Z 저크가 임펄스 진동→수직 벽면 잔상(ghosting)을 유발하던 문제 해결. 장비 프로파일 version → 1.5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon TPU-HS</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>isun3d TPU-HS(고속 TPU, Shore 95A) 추가. base + xCeler-I/Plus/Mini. fdm_filament_tpu 계열 베이스 신설. 초기값(노즐 230/230, 베드 50, 최대유량 5, 팬 100%) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Filament profile</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>신규 필라멘트: Cubicon Rainbow PLA HS</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>한일 Rainbow PLA High Speed (Bambu PLA HS 유사). base + xCeler-I/Plus/Mini, Cubicon PLA @base 상속. 초기값(노즐 220/215, 베드 60, 최대유량 28, flow 0.98) — 캘리브레이션 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>1.5.0-rc1</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Chore</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
           <t>Profile package</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>프로파일 패키지 버전 02.03.02.00 → 02.03.03.00</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Cubicon.json. 기설치 사용자에게 프로파일 갱신 전파를 위해 패키지 버전 상승 (신규 필라멘트·저크 반영).</t>
         </is>
